--- a/server/excel/release/resource-recovery.xlsx
+++ b/server/excel/release/resource-recovery.xlsx
@@ -1,121 +1,87 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9302"/>
-  <workbookPr defaultThemeVersion="124226"/>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <workbookPr/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12540"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="资源找回" sheetId="1" r:id="rId1"/>
+    <sheet name="资源找回" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="144525"/>
+  <definedNames/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="14">
-  <si>
-    <t>功能ID</t>
-  </si>
-  <si>
-    <t>排序</t>
-  </si>
-  <si>
-    <t>找回价格</t>
-  </si>
-  <si>
-    <t>功能名</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Thường ngày phó bản - Kim tệ</t>
-  </si>
-  <si>
-    <t>Thường ngày phó bản - Kinh nghiệm</t>
-  </si>
-  <si>
-    <t>Thường ngày phó bản - Anh hùng</t>
-  </si>
-  <si>
-    <t>Thường ngày phó bản - Pháp bảo</t>
-  </si>
-  <si>
-    <t>Thường ngày phó bản - Tỉ ấn</t>
-  </si>
-  <si>
-    <t>Sơn Hải kinh</t>
-  </si>
-  <si>
-    <t>Nhanh chóng tác chiến</t>
-  </si>
-  <si>
-    <t>Linh Lung Tháp</t>
-  </si>
-  <si>
-    <t>0:1:1000</t>
-  </si>
-  <si>
-    <t>0:1:2000</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
+  <si>
+    <t xml:space="preserve">功能ID</t>
+  </si>
+  <si>
+    <t xml:space="preserve">排序</t>
+  </si>
+  <si>
+    <t xml:space="preserve">找回价格</t>
+  </si>
+  <si>
+    <t xml:space="preserve">功能名</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0:1:1000</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Thường ngày phó bản - Kim tệ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Thường ngày phó bản - Kinh nghiệm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Thường ngày phó bản - Tướng</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Thường ngày phó bản - Pháp bảo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Thường ngày phó bản - Tỉ ấn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0:1:2000</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sơn Hải kinh</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nhanh chóng tác chiến</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linh Lung Tháp</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="5">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="1">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
+      <color theme="1"/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="3"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -123,85 +89,85 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
+  <cellStyleXfs count="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
+  <cellXfs count="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
-  <cellStyles count="2">
-    <cellStyle name="Calculation" xfId="1" builtinId="22"/>
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+  <cellStyles count="1">
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <dxfs count="2">
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-  </dxfs>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -280,7 +246,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -315,7 +280,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -491,149 +455,141 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:D9"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="9" style="1"/>
-    <col min="3" max="4" width="13" customWidth="1"/>
-  </cols>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:4">
-      <c r="A1" s="3" t="s">
+    <row r="1">
+      <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4">
-      <c r="A2" s="1">
+    <row r="2">
+      <c r="A2" t="n">
         <v>4001</v>
       </c>
-      <c r="B2" s="1">
+      <c r="B2" t="n">
         <v>1</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="C2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>4002</v>
+      </c>
+      <c r="B3" t="n">
+        <v>2</v>
+      </c>
+      <c r="C3" t="s">
+        <v>4</v>
+      </c>
+      <c r="D3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>4003</v>
+      </c>
+      <c r="B4" t="n">
+        <v>3</v>
+      </c>
+      <c r="C4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4004</v>
+      </c>
+      <c r="B5" t="n">
+        <v>4</v>
+      </c>
+      <c r="C5" t="s">
+        <v>4</v>
+      </c>
+      <c r="D5" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>4005</v>
+      </c>
+      <c r="B6" t="n">
+        <v>5</v>
+      </c>
+      <c r="C6" t="s">
+        <v>4</v>
+      </c>
+      <c r="D6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>5000</v>
+      </c>
+      <c r="B7" t="n">
+        <v>8</v>
+      </c>
+      <c r="C7" t="s">
+        <v>10</v>
+      </c>
+      <c r="D7" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>1004</v>
+      </c>
+      <c r="B8" t="n">
+        <v>6</v>
+      </c>
+      <c r="C8" t="s">
+        <v>10</v>
+      </c>
+      <c r="D8" t="s">
         <v>12</v>
       </c>
-      <c r="D2" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4">
-      <c r="A3" s="1">
-        <v>4002</v>
-      </c>
-      <c r="B3" s="1">
-        <v>2</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4">
-      <c r="A4" s="1">
-        <v>4003</v>
-      </c>
-      <c r="B4" s="1">
-        <v>3</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4">
-      <c r="A5" s="1">
-        <v>4004</v>
-      </c>
-      <c r="B5" s="1">
-        <v>4</v>
-      </c>
-      <c r="C5" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="D5" s="2" t="s">
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>1080</v>
+      </c>
+      <c r="B9" t="n">
         <v>7</v>
       </c>
-    </row>
-    <row r="6" spans="1:4">
-      <c r="A6" s="1">
-        <v>4005</v>
-      </c>
-      <c r="B6" s="1">
-        <v>5</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4">
-      <c r="A7" s="1">
-        <v>5000</v>
-      </c>
-      <c r="B7" s="1">
-        <v>8</v>
-      </c>
-      <c r="C7" s="4" t="s">
+      <c r="C9" t="s">
+        <v>4</v>
+      </c>
+      <c r="D9" t="s">
         <v>13</v>
       </c>
-      <c r="D7" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4">
-      <c r="A8" s="1">
-        <v>1004</v>
-      </c>
-      <c r="B8" s="1">
-        <v>6</v>
-      </c>
-      <c r="C8" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4">
-      <c r="A9" s="1">
-        <v>1080</v>
-      </c>
-      <c r="B9" s="1">
-        <v>7</v>
-      </c>
-      <c r="C9" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>11</v>
-      </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="3" type="noConversion"/>
-  <conditionalFormatting sqref="A2:A6">
-    <cfRule type="duplicateValues" dxfId="1" priority="2"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A7">
-    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
-  </conditionalFormatting>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>